--- a/data/trans_camb/P15-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P15-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 10,52</t>
+          <t>0,83; 10,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 3,93</t>
+          <t>-4,4; 3,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 7,27</t>
+          <t>-1,85; 8,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 8,15</t>
+          <t>-0,96; 8,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 9,48</t>
+          <t>0,01; 10,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 8,12</t>
+          <t>0,26; 8,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,5</t>
+          <t>1,25; 8,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,5</t>
+          <t>-1,27; 5,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 6,5</t>
+          <t>0,3; 6,44</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 227,41</t>
+          <t>8,08; 234,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 81,1</t>
+          <t>-50,56; 79,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 141,26</t>
+          <t>-25,85; 199,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 214,5</t>
+          <t>-17,58; 240,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 276,28</t>
+          <t>-3,66; 265,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 249,15</t>
+          <t>-1,05; 239,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,29; 173,85</t>
+          <t>13,65; 163,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 113,96</t>
+          <t>-18,37; 95,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 143,95</t>
+          <t>2,37; 129,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,01</t>
+          <t>-0,79; 4,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,35</t>
+          <t>-2,69; 2,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,57</t>
+          <t>-2,27; 3,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,06</t>
+          <t>-0,5; 4,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,51</t>
+          <t>-2,92; 1,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,4</t>
+          <t>0,44; 5,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,22</t>
+          <t>0,12; 4,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,41</t>
+          <t>-2,13; 1,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,93</t>
+          <t>-0,08; 3,64</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 186,37</t>
+          <t>-14,74; 195,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,25; 88,18</t>
+          <t>-51,08; 95,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 126,61</t>
+          <t>-43,68; 134,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 220,33</t>
+          <t>-14,01; 169,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,3; 57,86</t>
+          <t>-59,62; 79,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 229,08</t>
+          <t>6,7; 233,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 143,63</t>
+          <t>1,98; 132,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,19; 49,73</t>
+          <t>-44,58; 48,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 133,82</t>
+          <t>-2,83; 123,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,42</t>
+          <t>0,93; 11,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 1,3</t>
+          <t>-6,96; 1,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 1,05</t>
+          <t>-7,41; 1,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 11,73</t>
+          <t>3,4; 11,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,64</t>
+          <t>-3,49; 2,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 6,3</t>
+          <t>0,08; 6,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,43</t>
+          <t>3,31; 10,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,38</t>
+          <t>-4,23; 1,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,59</t>
+          <t>-2,69; 2,57</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,75; 154,52</t>
+          <t>6,46; 151,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 20,79</t>
+          <t>-56,31; 28,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,24; 18,7</t>
+          <t>-59,11; 23,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49,39; 387,17</t>
+          <t>48,97; 362,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 90,72</t>
+          <t>-58,2; 93,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 215,5</t>
+          <t>-0,69; 214,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,99; 182,71</t>
+          <t>34,89; 170,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,83; 24,4</t>
+          <t>-49,0; 16,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 44,55</t>
+          <t>-30,24; 47,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 1,96</t>
+          <t>-7,09; 2,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 3,7</t>
+          <t>-5,55; 4,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 2,28</t>
+          <t>-8,53; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,95</t>
+          <t>-4,26; 2,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 8,11</t>
+          <t>0,14; 7,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 1,57</t>
+          <t>-4,82; 1,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 1,1</t>
+          <t>-4,47; 1,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,02</t>
+          <t>-1,7; 4,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,17</t>
+          <t>-5,98; 0,26</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,14; 20,81</t>
+          <t>-51,52; 30,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,87; 41,71</t>
+          <t>-42,26; 47,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,33; 31,09</t>
+          <t>-65,08; 27,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,59; 51,59</t>
+          <t>-59,22; 70,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 198,99</t>
+          <t>-1,05; 206,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 47,54</t>
+          <t>-68,25; 47,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 16,7</t>
+          <t>-45,75; 19,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 75,22</t>
+          <t>-17,64; 69,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,17; 3,19</t>
+          <t>-63,19; 4,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 1,5</t>
+          <t>-9,18; 1,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -0,39</t>
+          <t>-10,4; 0,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -0,4</t>
+          <t>-10,52; -0,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 8,05</t>
+          <t>-2,35; 7,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,55; -0,57</t>
+          <t>-8,29; -0,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,8; -2,98</t>
+          <t>-10,68; -2,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,44</t>
+          <t>-3,48; 3,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,95; -1,47</t>
+          <t>-7,86; -1,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; -2,9</t>
+          <t>-9,41; -3,07</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,22; 25,64</t>
+          <t>-68,94; 34,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-78,39; 0,45</t>
+          <t>-76,52; 18,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,36; 4,73</t>
+          <t>-82,74; -0,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 216,04</t>
+          <t>-32,26; 203,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-92,45; 15,7</t>
+          <t>-91,99; 29,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -69,72</t>
+          <t>-100,0; -61,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 56,24</t>
+          <t>-37,21; 67,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-77,8; -17,73</t>
+          <t>-77,76; -17,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-89,42; -41,38</t>
+          <t>-89,95; -45,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 8,75</t>
+          <t>-1,45; 8,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 8,72</t>
+          <t>-1,35; 8,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 6,85</t>
+          <t>-1,84; 7,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 9,8</t>
+          <t>-0,28; 10,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,45; 11,38</t>
+          <t>0,64; 11,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 6,88</t>
+          <t>-1,43; 6,94</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,5</t>
+          <t>0,91; 7,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,68</t>
+          <t>0,68; 8,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,81</t>
+          <t>-0,67; 5,61</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 172,0</t>
+          <t>-18,09; 176,39</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 177,97</t>
+          <t>-15,95; 171,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 137,59</t>
+          <t>-22,28; 148,71</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 169,22</t>
+          <t>-4,74; 186,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 200,09</t>
+          <t>2,48; 204,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 132,05</t>
+          <t>-15,59; 127,61</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,99; 144,09</t>
+          <t>9,92; 131,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>12,69; 152,97</t>
+          <t>7,05; 132,71</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 99,28</t>
+          <t>-7,91; 97,79</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,66</t>
+          <t>-0,81; 5,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,98; -0,8</t>
+          <t>-6,23; -0,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,92</t>
+          <t>-3,66; 2,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,56</t>
+          <t>2,29; 7,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,36</t>
+          <t>-1,98; 2,4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 4,99</t>
+          <t>-2,45; 5,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,88</t>
+          <t>1,82; 5,94</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,08</t>
+          <t>-3,23; 0,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,89</t>
+          <t>-2,04; 2,94</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 97,61</t>
+          <t>-9,45; 104,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,14; -11,82</t>
+          <t>-67,47; -6,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 52,07</t>
+          <t>-41,21; 49,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40,01; 260,51</t>
+          <t>35,75; 272,85</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 87,23</t>
+          <t>-45,48; 93,82</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 167,05</t>
+          <t>-40,62; 160,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,45; 122,76</t>
+          <t>27,92; 132,46</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 2,83</t>
+          <t>-50,45; 1,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 59,51</t>
+          <t>-32,26; 60,99</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -1,11</t>
+          <t>-5,96; -1,34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,03</t>
+          <t>-4,45; 0,09</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,68; -1,47</t>
+          <t>-6,39; -1,56</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,06; -0,87</t>
+          <t>-4,96; -0,69</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,71</t>
+          <t>-4,79; -0,73</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -0,03</t>
+          <t>-4,27; -0,11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,87; -1,69</t>
+          <t>-4,63; -1,58</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -1,0</t>
+          <t>-4,09; -1,06</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -1,55</t>
+          <t>-4,84; -1,3</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-74,02; -21,63</t>
+          <t>-72,58; -22,06</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-56,22; 2,88</t>
+          <t>-56,71; 3,12</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-84,33; -27,58</t>
+          <t>-82,93; -27,15</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-67,89; -13,76</t>
+          <t>-68,2; -9,76</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-66,79; -11,29</t>
+          <t>-67,03; -14,31</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-58,7; -1,56</t>
+          <t>-57,23; 0,25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-66,35; -31,17</t>
+          <t>-64,15; -26,91</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-55,56; -15,04</t>
+          <t>-56,35; -17,42</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-68,99; -27,27</t>
+          <t>-69,08; -26,02</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,41</t>
+          <t>-0,28; 2,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,32</t>
+          <t>-2,71; -0,29</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,23</t>
+          <t>-3,3; -0,26</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,24</t>
+          <t>0,88; 3,18</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,36</t>
+          <t>-0,94; 1,28</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,92</t>
+          <t>-0,62; 1,71</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,4</t>
+          <t>0,65; 2,44</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,24</t>
+          <t>-1,39; 0,19</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,45</t>
+          <t>-1,6; 0,45</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 36,24</t>
+          <t>-3,48; 32,82</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-34,96; -5,06</t>
+          <t>-33,32; -3,96</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,03; -3,14</t>
+          <t>-41,11; -3,8</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>12,14; 67,82</t>
+          <t>15,42; 67,5</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 29,61</t>
+          <t>-15,8; 27,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 40,77</t>
+          <t>-10,95; 36,65</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,49; 41,1</t>
+          <t>9,39; 41,84</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 4,09</t>
+          <t>-21,22; 3,2</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 7,79</t>
+          <t>-24,27; 7,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P15-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>2,73</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 10,8</t>
+          <t>1,38; 10,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,67</t>
+          <t>-3,89; 4,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 8,86</t>
+          <t>-2,73; 6,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 8,82</t>
+          <t>-0,68; 8,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 10,01</t>
+          <t>0,22; 9,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 8,08</t>
+          <t>-0,37; 7,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,11</t>
+          <t>1,61; 8,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,12</t>
+          <t>-0,69; 5,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,44</t>
+          <t>-0,19; 5,61</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 234,67</t>
+          <t>14,06; 234,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 79,23</t>
+          <t>-46,44; 80,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 199,1</t>
+          <t>-31,1; 135,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 240,3</t>
+          <t>-13,22; 262,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 265,78</t>
+          <t>-1,65; 297,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 239,37</t>
+          <t>-5,22; 245,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,65; 163,35</t>
+          <t>21,33; 181,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 95,73</t>
+          <t>-9,76; 107,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 129,89</t>
+          <t>-4,8; 110,25</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>1,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,98</t>
+          <t>-0,42; 5,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,43</t>
+          <t>-2,88; 2,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,67</t>
+          <t>-2,14; 3,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,7</t>
+          <t>-0,55; 4,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,77</t>
+          <t>-3,15; 1,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,52</t>
+          <t>0,13; 5,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,12</t>
+          <t>0,32; 4,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,29</t>
+          <t>-2,11; 1,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,64</t>
+          <t>-0,19; 3,52</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 195,51</t>
+          <t>-8,72; 182,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,08; 95,42</t>
+          <t>-52,32; 99,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 134,85</t>
+          <t>-41,64; 130,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 169,44</t>
+          <t>-11,63; 188,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,62; 79,9</t>
+          <t>-63,51; 63,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 233,22</t>
+          <t>0,2; 202,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 132,51</t>
+          <t>5,09; 151,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 48,7</t>
+          <t>-45,5; 46,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 123,13</t>
+          <t>-4,02; 116,5</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,12</t>
+          <t>-2,81</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 11,3</t>
+          <t>1,42; 10,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,72</t>
+          <t>-7,2; 1,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 1,49</t>
+          <t>-7,37; 1,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 11,84</t>
+          <t>3,37; 11,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,56</t>
+          <t>-3,68; 2,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 6,29</t>
+          <t>-0,38; 6,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,04</t>
+          <t>3,78; 10,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,08</t>
+          <t>-4,59; 1,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,57</t>
+          <t>-2,73; 2,71</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-31,64%</t>
+          <t>-28,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 151,33</t>
+          <t>10,03; 151,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 28,55</t>
+          <t>-58,1; 19,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,11; 23,95</t>
+          <t>-58,96; 23,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48,97; 362,91</t>
+          <t>42,1; 388,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 93,55</t>
+          <t>-58,59; 82,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 214,74</t>
+          <t>-8,62; 191,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,89; 170,86</t>
+          <t>41,14; 187,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 16,23</t>
+          <t>-52,17; 21,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 47,28</t>
+          <t>-30,49; 46,87</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-0,92</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-2,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,66</t>
+          <t>-6,72; 2,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 4,11</t>
+          <t>-5,07; 3,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 2,16</t>
+          <t>-8,2; 1,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 2,16</t>
+          <t>-4,28; 2,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 7,98</t>
+          <t>-0,21; 8,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,8</t>
+          <t>-4,06; 2,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 1,19</t>
+          <t>-4,74; 1,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,87</t>
+          <t>-1,31; 4,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 0,26</t>
+          <t>-5,25; 1,06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-31,43%</t>
+          <t>-32,06%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-30,67%</t>
+          <t>-16,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-35,5%</t>
+          <t>-27,63%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,52; 30,82</t>
+          <t>-50,63; 34,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 47,31</t>
+          <t>-39,51; 42,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 27,89</t>
+          <t>-63,35; 23,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 70,77</t>
+          <t>-58,82; 53,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 206,13</t>
+          <t>-3,95; 204,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,25; 47,27</t>
+          <t>-58,34; 75,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 19,59</t>
+          <t>-47,94; 16,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 69,96</t>
+          <t>-14,59; 68,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,19; 4,41</t>
+          <t>-54,84; 15,43</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>-5,95</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,89</t>
+          <t>-5,92</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,88</t>
+          <t>-6,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 1,76</t>
+          <t>-9,22; 1,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 0,71</t>
+          <t>-10,69; -0,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,52; -0,59</t>
+          <t>-11,06; -1,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 7,95</t>
+          <t>-2,16; 8,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,29; -0,34</t>
+          <t>-8,36; -0,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -2,93</t>
+          <t>-10,67; -3,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,71</t>
+          <t>-4,21; 3,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,86; -1,4</t>
+          <t>-7,78; -1,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -3,07</t>
+          <t>-9,22; -3,23</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-58,5%</t>
+          <t>-62,01%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-95,79%</t>
+          <t>-96,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-74,84%</t>
+          <t>-76,42%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,94; 34,56</t>
+          <t>-69,63; 27,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-76,52; 18,03</t>
+          <t>-78,15; 3,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-82,74; -0,44</t>
+          <t>-83,78; -1,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 203,14</t>
+          <t>-30,23; 213,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-91,99; 29,94</t>
+          <t>-90,91; 13,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -61,0</t>
+          <t>-100,0; -61,95</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 67,29</t>
+          <t>-41,78; 53,81</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-77,76; -17,74</t>
+          <t>-77,01; -17,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-89,95; -45,62</t>
+          <t>-90,1; -51,4</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>2,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 8,79</t>
+          <t>-1,12; 9,25</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 8,36</t>
+          <t>-1,6; 8,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 7,05</t>
+          <t>-2,05; 6,78</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 10,33</t>
+          <t>-0,15; 9,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,64; 11,1</t>
+          <t>0,25; 11,02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,94</t>
+          <t>-1,45; 7,15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,82</t>
+          <t>0,66; 8,04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 8,16</t>
+          <t>1,0; 8,31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,61</t>
+          <t>-0,54; 5,66</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 176,39</t>
+          <t>-14,56; 178,32</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 171,69</t>
+          <t>-20,36; 171,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 148,71</t>
+          <t>-22,4; 132,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 186,47</t>
+          <t>-9,75; 180,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,48; 204,7</t>
+          <t>-0,99; 196,73</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 127,61</t>
+          <t>-15,87; 136,69</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,92; 131,03</t>
+          <t>4,94; 133,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,05; 132,71</t>
+          <t>9,22; 144,35</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 97,79</t>
+          <t>-6,54; 99,45</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>2,13</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 5,87</t>
+          <t>-0,55; 6,12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -0,6</t>
+          <t>-6,0; -0,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,78</t>
+          <t>-2,61; 3,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,44</t>
+          <t>2,27; 7,68</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,4</t>
+          <t>-2,1; 2,28</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 5,08</t>
+          <t>1,6; 6,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,94</t>
+          <t>1,78; 5,59</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,04</t>
+          <t>-3,15; 0,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,94</t>
+          <t>0,23; 4,34</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-5,21%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>100,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 104,29</t>
+          <t>-6,89; 102,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,47; -6,49</t>
+          <t>-67,47; -9,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 49,38</t>
+          <t>-30,05; 67,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>35,75; 272,85</t>
+          <t>42,62; 277,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-45,48; 93,82</t>
+          <t>-42,52; 78,69</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 160,06</t>
+          <t>29,46; 219,64</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,92; 132,46</t>
+          <t>28,9; 128,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-50,45; 1,48</t>
+          <t>-48,65; 4,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 60,99</t>
+          <t>3,06; 94,67</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,76</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-2,03</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-2,43</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -1,34</t>
+          <t>-5,66; -1,27</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,09</t>
+          <t>-4,49; 0,35</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -1,56</t>
+          <t>-5,07; -0,54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,96; -0,69</t>
+          <t>-5,13; -0,86</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,79; -0,73</t>
+          <t>-5,13; -1,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,27; -0,11</t>
+          <t>-4,33; -0,1</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -1,58</t>
+          <t>-4,65; -1,53</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -1,06</t>
+          <t>-4,0; -0,9</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,84; -1,3</t>
+          <t>-3,91; -0,83</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-57,34%</t>
+          <t>-43,46%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-34,64%</t>
+          <t>-33,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-47,56%</t>
+          <t>-38,44%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-72,58; -22,06</t>
+          <t>-70,55; -21,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 3,12</t>
+          <t>-55,79; 6,9</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-82,93; -27,15</t>
+          <t>-65,95; -11,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-68,2; -9,76</t>
+          <t>-70,05; -14,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-67,03; -14,31</t>
+          <t>-66,56; -18,71</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 0,25</t>
+          <t>-56,88; -0,89</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-64,15; -26,91</t>
+          <t>-64,23; -27,26</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-56,35; -17,42</t>
+          <t>-55,51; -15,98</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-69,08; -26,02</t>
+          <t>-54,64; -15,28</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,22</t>
+          <t>-0,29; 2,41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -0,29</t>
+          <t>-2,8; -0,31</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,26</t>
+          <t>-2,33; 0,28</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,18</t>
+          <t>0,87; 3,23</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,28</t>
+          <t>-0,88; 1,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,71</t>
+          <t>-0,07; 1,97</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,44</t>
+          <t>0,58; 2,46</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,19</t>
+          <t>-1,45; 0,27</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,45</t>
+          <t>-0,74; 0,89</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-22,05%</t>
+          <t>-15,66%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-7,62%</t>
+          <t>-0,82%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 32,82</t>
+          <t>-3,56; 36,06</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-33,32; -3,96</t>
+          <t>-34,67; -4,88</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,11; -3,8</t>
+          <t>-29,32; 3,82</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>15,42; 67,5</t>
+          <t>14,68; 68,54</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 27,4</t>
+          <t>-15,39; 27,67</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 36,65</t>
+          <t>-1,29; 42,93</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,39; 41,84</t>
+          <t>8,68; 41,73</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 3,2</t>
+          <t>-21,5; 4,44</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 7,37</t>
+          <t>-11,23; 14,87</t>
         </is>
       </c>
     </row>
